--- a/nostoc.xlsx
+++ b/nostoc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10913"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\OneDrive\Universita\Magistrale\2025-2026\Iterazione\Progetto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonio/Dropbox/2_Didattica/02 LM - Iterazione/2026/Lavori di Gruppo/nostoc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B6C25F-15A7-44A4-A64F-DB71E45373C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C38B13-F4A7-0C4E-BE5C-477D66437B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1300" yWindow="500" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>#</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Var. Y</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>Var. T</t>
@@ -275,7 +278,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -554,13 +557,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:O374"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="6" width="9.140625" style="1"/>
-    <col min="7" max="7" width="9.140625" style="10"/>
+    <col min="2" max="6" width="9.1640625" style="1"/>
+    <col min="7" max="7" width="9.1640625" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
@@ -570,13 +573,13 @@
       <c r="D2" s="19"/>
       <c r="E2" s="20"/>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="22"/>
       <c r="C3" s="5" t="s">
         <v>1</v>
@@ -594,7 +597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -614,7 +617,7 @@
         <v>0.28599999999999998</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="17">
         <v>2</v>
       </c>
@@ -634,7 +637,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="17">
         <v>3</v>
       </c>
@@ -654,7 +657,7 @@
         <v>0.54400000000000004</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="17">
         <v>4</v>
       </c>
@@ -674,7 +677,7 @@
         <v>0.79600000000000004</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="17">
         <v>5</v>
       </c>
@@ -694,7 +697,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="17">
         <v>6</v>
       </c>
@@ -714,7 +717,7 @@
         <v>1.444</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="16">
         <v>7</v>
       </c>
@@ -734,7 +737,7 @@
         <v>1.9079999999999999</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="15">
         <v>8</v>
       </c>
@@ -754,7 +757,7 @@
         <v>0.27700000000000002</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="17">
         <v>9</v>
       </c>
@@ -774,7 +777,7 @@
         <v>0.46500000000000002</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="17">
         <v>10</v>
       </c>
@@ -794,7 +797,7 @@
         <v>0.50600000000000001</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="17">
         <v>11</v>
       </c>
@@ -814,7 +817,7 @@
         <v>0.78800000000000003</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="17">
         <v>12</v>
       </c>
@@ -834,7 +837,7 @@
         <v>1.198</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="17">
         <v>13</v>
       </c>
@@ -854,7 +857,7 @@
         <v>1.4259999999999999</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="16">
         <v>14</v>
       </c>
@@ -874,7 +877,7 @@
         <v>1.9319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="15">
         <v>15</v>
       </c>
@@ -894,7 +897,7 @@
         <v>0.29399999999999998</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="17">
         <v>16</v>
       </c>
@@ -914,7 +917,7 @@
         <v>0.39700000000000002</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="17">
         <v>17</v>
       </c>
@@ -934,7 +937,7 @@
         <v>0.52400000000000002</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="17">
         <v>18</v>
       </c>
@@ -954,7 +957,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22" s="17">
         <v>19</v>
       </c>
@@ -974,7 +977,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="17">
         <v>20</v>
       </c>
@@ -994,7 +997,7 @@
         <v>1.3220000000000001</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="16">
         <v>21</v>
       </c>
@@ -1014,7 +1017,7 @@
         <v>1.6519999999999999</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="15">
         <v>22</v>
       </c>
@@ -1034,7 +1037,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="17">
         <v>23</v>
       </c>
@@ -1054,7 +1057,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="17">
         <v>24</v>
       </c>
@@ -1074,7 +1077,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="17">
         <v>25</v>
       </c>
@@ -1094,7 +1097,7 @@
         <v>1.0620000000000001</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="17">
         <v>26</v>
       </c>
@@ -1114,7 +1117,7 @@
         <v>1.546</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="17">
         <v>27</v>
       </c>
@@ -1134,7 +1137,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="16">
         <v>28</v>
       </c>
@@ -1154,7 +1157,7 @@
         <v>2.7759999999999998</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="15">
         <v>29</v>
       </c>
@@ -1174,7 +1177,7 @@
         <v>0.371</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="17">
         <v>30</v>
       </c>
@@ -1194,7 +1197,7 @@
         <v>0.51100000000000001</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="17">
         <v>31</v>
       </c>
@@ -1214,7 +1217,7 @@
         <v>0.57199999999999995</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="17">
         <v>32</v>
       </c>
@@ -1234,7 +1237,7 @@
         <v>0.99399999999999999</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36" s="17">
         <v>33</v>
       </c>
@@ -1254,7 +1257,7 @@
         <v>1.464</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="17">
         <v>34</v>
       </c>
@@ -1274,7 +1277,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="16">
         <v>35</v>
       </c>
@@ -1294,7 +1297,7 @@
         <v>2.6480000000000001</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="15">
         <v>36</v>
       </c>
@@ -1314,7 +1317,7 @@
         <v>0.40200000000000002</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="17">
         <v>37</v>
       </c>
@@ -1334,7 +1337,7 @@
         <v>0.52800000000000002</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="17">
         <v>38</v>
       </c>
@@ -1354,7 +1357,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="17">
         <v>39</v>
       </c>
@@ -1374,7 +1377,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="17">
         <v>40</v>
       </c>
@@ -1394,7 +1397,7 @@
         <v>1.3140000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="17">
         <v>41</v>
       </c>
@@ -1414,7 +1417,7 @@
         <v>1.992</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45" s="16">
         <v>42</v>
       </c>
@@ -1434,7 +1437,7 @@
         <v>2.3959999999999999</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="15">
         <v>43</v>
       </c>
@@ -1454,7 +1457,7 @@
         <v>0.36299999999999999</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B47" s="17">
         <v>44</v>
       </c>
@@ -1474,7 +1477,7 @@
         <v>0.48499999999999999</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="17">
         <v>45</v>
       </c>
@@ -1494,7 +1497,7 @@
         <v>0.63200000000000001</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B49" s="17">
         <v>46</v>
       </c>
@@ -1514,7 +1517,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="17">
         <v>47</v>
       </c>
@@ -1534,7 +1537,7 @@
         <v>1.6319999999999999</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B51" s="17">
         <v>48</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>2.536</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="16">
         <v>49</v>
       </c>
@@ -1574,7 +1577,7 @@
         <v>3.2280000000000002</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B53" s="15">
         <v>50</v>
       </c>
@@ -1594,7 +1597,7 @@
         <v>0.36199999999999999</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B54" s="17">
         <v>51</v>
       </c>
@@ -1614,7 +1617,7 @@
         <v>0.52300000000000002</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B55" s="17">
         <v>52</v>
       </c>
@@ -1634,7 +1637,7 @@
         <v>0.626</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B56" s="17">
         <v>53</v>
       </c>
@@ -1654,7 +1657,7 @@
         <v>1.1240000000000001</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B57" s="17">
         <v>54</v>
       </c>
@@ -1674,7 +1677,7 @@
         <v>1.5840000000000001</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B58" s="17">
         <v>55</v>
       </c>
@@ -1694,7 +1697,7 @@
         <v>2.5920000000000001</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B59" s="16">
         <v>56</v>
       </c>
@@ -1714,7 +1717,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B60" s="15">
         <v>57</v>
       </c>
@@ -1734,7 +1737,7 @@
         <v>0.36599999999999999</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B61" s="17">
         <v>58</v>
       </c>
@@ -1754,7 +1757,7 @@
         <v>0.48199999999999998</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B62" s="17">
         <v>59</v>
       </c>
@@ -1774,7 +1777,7 @@
         <v>0.58799999999999997</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B63" s="17">
         <v>60</v>
       </c>
@@ -1794,7 +1797,7 @@
         <v>1.002</v>
       </c>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B64" s="17">
         <v>61</v>
       </c>
@@ -1814,7 +1817,7 @@
         <v>1.464</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B65" s="17">
         <v>62</v>
       </c>
@@ -1834,7 +1837,7 @@
         <v>2.3919999999999999</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B66" s="16">
         <v>63</v>
       </c>
@@ -1854,7 +1857,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B67" s="15">
         <v>64</v>
       </c>
@@ -1874,7 +1877,7 @@
         <v>0.38700000000000001</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B68" s="17">
         <v>65</v>
       </c>
@@ -1894,7 +1897,7 @@
         <v>0.42099999999999999</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B69" s="17">
         <v>66</v>
       </c>
@@ -1914,7 +1917,7 @@
         <v>0.68899999999999995</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B70" s="17">
         <v>67</v>
       </c>
@@ -1934,7 +1937,7 @@
         <v>1.3480000000000001</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B71" s="17">
         <v>68</v>
       </c>
@@ -1954,7 +1957,7 @@
         <v>1.748</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B72" s="17">
         <v>69</v>
       </c>
@@ -1974,7 +1977,7 @@
         <v>2.3820000000000001</v>
       </c>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B73" s="16">
         <v>70</v>
       </c>
@@ -1994,7 +1997,7 @@
         <v>3.1040000000000001</v>
       </c>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B74" s="15">
         <v>71</v>
       </c>
@@ -2014,7 +2017,7 @@
         <v>0.34100000000000003</v>
       </c>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B75" s="17">
         <v>72</v>
       </c>
@@ -2034,7 +2037,7 @@
         <v>0.48599999999999999</v>
       </c>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B76" s="17">
         <v>73</v>
       </c>
@@ -2054,7 +2057,7 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B77" s="17">
         <v>74</v>
       </c>
@@ -2074,7 +2077,7 @@
         <v>1.456</v>
       </c>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B78" s="17">
         <v>75</v>
       </c>
@@ -2094,7 +2097,7 @@
         <v>2.0190000000000001</v>
       </c>
     </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B79" s="17">
         <v>76</v>
       </c>
@@ -2114,7 +2117,7 @@
         <v>2.552</v>
       </c>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B80" s="16">
         <v>77</v>
       </c>
@@ -2134,7 +2137,7 @@
         <v>2.9449999999999998</v>
       </c>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B81" s="15">
         <v>78</v>
       </c>
@@ -2154,7 +2157,7 @@
         <v>0.313</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B82" s="17">
         <v>79</v>
       </c>
@@ -2174,7 +2177,7 @@
         <v>0.39700000000000002</v>
       </c>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B83" s="17">
         <v>80</v>
       </c>
@@ -2194,7 +2197,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B84" s="17">
         <v>81</v>
       </c>
@@ -2214,7 +2217,7 @@
         <v>1.395</v>
       </c>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B85" s="17">
         <v>82</v>
       </c>
@@ -2234,7 +2237,7 @@
         <v>1.8959999999999999</v>
       </c>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B86" s="17">
         <v>83</v>
       </c>
@@ -2254,7 +2257,7 @@
         <v>2.3449999999999998</v>
       </c>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B87" s="16">
         <v>84</v>
       </c>
@@ -2270,9 +2273,11 @@
       <c r="F87" s="7">
         <v>6</v>
       </c>
-      <c r="G87" s="13"/>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G87" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B88" s="15">
         <v>85</v>
       </c>
@@ -2292,7 +2297,7 @@
         <v>0.32900000000000001</v>
       </c>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B89" s="17">
         <v>86</v>
       </c>
@@ -2312,7 +2317,7 @@
         <v>0.40799999999999997</v>
       </c>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B90" s="17">
         <v>87</v>
       </c>
@@ -2332,7 +2337,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B91" s="17">
         <v>88</v>
       </c>
@@ -2352,7 +2357,7 @@
         <v>1.3979999999999999</v>
       </c>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B92" s="17">
         <v>89</v>
       </c>
@@ -2372,7 +2377,7 @@
         <v>2.4060000000000001</v>
       </c>
     </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B93" s="17">
         <v>90</v>
       </c>
@@ -2392,7 +2397,7 @@
         <v>3.4279999999999999</v>
       </c>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B94" s="16">
         <v>91</v>
       </c>
@@ -2412,7 +2417,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B95" s="15">
         <v>92</v>
       </c>
@@ -2432,7 +2437,7 @@
         <v>0.311</v>
       </c>
     </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B96" s="17">
         <v>93</v>
       </c>
@@ -2452,7 +2457,7 @@
         <v>0.39700000000000002</v>
       </c>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B97" s="17">
         <v>94</v>
       </c>
@@ -2472,7 +2477,7 @@
         <v>0.66900000000000004</v>
       </c>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B98" s="17">
         <v>95</v>
       </c>
@@ -2492,7 +2497,7 @@
         <v>1.456</v>
       </c>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B99" s="17">
         <v>96</v>
       </c>
@@ -2512,7 +2517,7 @@
         <v>2.3340000000000001</v>
       </c>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B100" s="17">
         <v>97</v>
       </c>
@@ -2532,7 +2537,7 @@
         <v>3.3119999999999998</v>
       </c>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B101" s="16">
         <v>98</v>
       </c>
@@ -2552,7 +2557,7 @@
         <v>4.1899999999999995</v>
       </c>
     </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B102" s="15">
         <v>99</v>
       </c>
@@ -2572,7 +2577,7 @@
         <v>0.253</v>
       </c>
     </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B103" s="17">
         <v>100</v>
       </c>
@@ -2592,7 +2597,7 @@
         <v>0.35399999999999998</v>
       </c>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B104" s="17">
         <v>101</v>
       </c>
@@ -2612,7 +2617,7 @@
         <v>0.54300000000000004</v>
       </c>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B105" s="17">
         <v>102</v>
       </c>
@@ -2632,7 +2637,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B106" s="17">
         <v>103</v>
       </c>
@@ -2652,7 +2657,7 @@
         <v>2.1640000000000001</v>
       </c>
     </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B107" s="17">
         <v>104</v>
       </c>
@@ -2672,7 +2677,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B108" s="16">
         <v>105</v>
       </c>
@@ -2688,9 +2693,11 @@
       <c r="F108" s="7">
         <v>6</v>
       </c>
-      <c r="G108" s="13"/>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G108" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B109" s="15">
         <v>106</v>
       </c>
@@ -2710,7 +2717,7 @@
         <v>0.33200000000000002</v>
       </c>
     </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B110" s="17">
         <v>107</v>
       </c>
@@ -2730,7 +2737,7 @@
         <v>0.47099999999999997</v>
       </c>
     </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B111" s="17">
         <v>108</v>
       </c>
@@ -2750,7 +2757,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B112" s="17">
         <v>109</v>
       </c>
@@ -2770,7 +2777,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B113" s="17">
         <v>110</v>
       </c>
@@ -2790,7 +2797,7 @@
         <v>2.3940000000000001</v>
       </c>
     </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B114" s="17">
         <v>111</v>
       </c>
@@ -2810,7 +2817,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B115" s="16">
         <v>112</v>
       </c>
@@ -2830,7 +2837,7 @@
         <v>4.0049999999999999</v>
       </c>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B116" s="15">
         <v>113</v>
       </c>
@@ -2850,7 +2857,7 @@
         <v>0.28399999999999997</v>
       </c>
     </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B117" s="17">
         <v>114</v>
       </c>
@@ -2870,7 +2877,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B118" s="17">
         <v>115</v>
       </c>
@@ -2890,7 +2897,7 @@
         <v>0.56799999999999995</v>
       </c>
     </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B119" s="17">
         <v>116</v>
       </c>
@@ -2910,7 +2917,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B120" s="17">
         <v>117</v>
       </c>
@@ -2930,7 +2937,7 @@
         <v>2.0580000000000003</v>
       </c>
     </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B121" s="17">
         <v>118</v>
       </c>
@@ -2950,7 +2957,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B122" s="16">
         <v>119</v>
       </c>
@@ -2970,7 +2977,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B123" s="15">
         <v>120</v>
       </c>
@@ -2990,7 +2997,7 @@
         <v>0.28699999999999998</v>
       </c>
     </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B124" s="17">
         <v>121</v>
       </c>
@@ -3010,7 +3017,7 @@
         <v>0.35899999999999999</v>
       </c>
     </row>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B125" s="17">
         <v>122</v>
       </c>
@@ -3030,7 +3037,7 @@
         <v>0.499</v>
       </c>
     </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B126" s="17">
         <v>123</v>
       </c>
@@ -3050,7 +3057,7 @@
         <v>1.028</v>
       </c>
     </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B127" s="17">
         <v>124</v>
       </c>
@@ -3070,7 +3077,7 @@
         <v>1.8780000000000001</v>
       </c>
     </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B128" s="17">
         <v>125</v>
       </c>
@@ -3090,7 +3097,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B129" s="16">
         <v>126</v>
       </c>
@@ -3110,7 +3117,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B130" s="15">
         <v>127</v>
       </c>
@@ -3130,7 +3137,7 @@
         <v>0.41399999999999998</v>
       </c>
     </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B131" s="17">
         <v>128</v>
       </c>
@@ -3150,7 +3157,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="132" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B132" s="17">
         <v>129</v>
       </c>
@@ -3170,7 +3177,7 @@
         <v>0.88800000000000001</v>
       </c>
     </row>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B133" s="17">
         <v>130</v>
       </c>
@@ -3190,7 +3197,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B134" s="17">
         <v>131</v>
       </c>
@@ -3210,7 +3217,7 @@
         <v>2.5880000000000001</v>
       </c>
     </row>
-    <row r="135" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B135" s="17">
         <v>132</v>
       </c>
@@ -3230,7 +3237,7 @@
         <v>4.7359999999999998</v>
       </c>
     </row>
-    <row r="136" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B136" s="16">
         <v>133</v>
       </c>
@@ -3250,7 +3257,7 @@
         <v>5.8699999999999992</v>
       </c>
     </row>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B137" s="15">
         <v>134</v>
       </c>
@@ -3270,7 +3277,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B138" s="17">
         <v>135</v>
       </c>
@@ -3290,7 +3297,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B139" s="17">
         <v>136</v>
       </c>
@@ -3310,7 +3317,7 @@
         <v>0.63400000000000001</v>
       </c>
     </row>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B140" s="17">
         <v>137</v>
       </c>
@@ -3330,7 +3337,7 @@
         <v>1.3160000000000001</v>
       </c>
     </row>
-    <row r="141" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B141" s="17">
         <v>138</v>
       </c>
@@ -3350,7 +3357,7 @@
         <v>2.4449999999999998</v>
       </c>
     </row>
-    <row r="142" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B142" s="17">
         <v>139</v>
       </c>
@@ -3370,7 +3377,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="143" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B143" s="16">
         <v>140</v>
       </c>
@@ -3390,7 +3397,7 @@
         <v>5.6079999999999997</v>
       </c>
     </row>
-    <row r="144" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B144" s="15">
         <v>141</v>
       </c>
@@ -3410,7 +3417,7 @@
         <v>0.40899999999999997</v>
       </c>
     </row>
-    <row r="145" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B145" s="17">
         <v>142</v>
       </c>
@@ -3430,7 +3437,7 @@
         <v>0.50900000000000001</v>
       </c>
     </row>
-    <row r="146" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B146" s="17">
         <v>143</v>
       </c>
@@ -3450,7 +3457,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="147" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B147" s="17">
         <v>144</v>
       </c>
@@ -3470,7 +3477,7 @@
         <v>1.4359999999999999</v>
       </c>
     </row>
-    <row r="148" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B148" s="17">
         <v>145</v>
       </c>
@@ -3490,7 +3497,7 @@
         <v>2.5229999999999997</v>
       </c>
     </row>
-    <row r="149" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B149" s="17">
         <v>146</v>
       </c>
@@ -3510,7 +3517,7 @@
         <v>3.6280000000000001</v>
       </c>
     </row>
-    <row r="150" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B150" s="16">
         <v>147</v>
       </c>
@@ -3530,7 +3537,7 @@
         <v>5.4160000000000004</v>
       </c>
     </row>
-    <row r="151" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B151" s="15">
         <v>148</v>
       </c>
@@ -3550,7 +3557,7 @@
         <v>0.39400000000000002</v>
       </c>
     </row>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B152" s="17">
         <v>149</v>
       </c>
@@ -3570,7 +3577,7 @@
         <v>0.47899999999999998</v>
       </c>
     </row>
-    <row r="153" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B153" s="17">
         <v>150</v>
       </c>
@@ -3590,7 +3597,7 @@
         <v>0.754</v>
       </c>
     </row>
-    <row r="154" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B154" s="17">
         <v>151</v>
       </c>
@@ -3610,7 +3617,7 @@
         <v>1.3859999999999999</v>
       </c>
     </row>
-    <row r="155" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B155" s="17">
         <v>152</v>
       </c>
@@ -3630,7 +3637,7 @@
         <v>2.2949999999999999</v>
       </c>
     </row>
-    <row r="156" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B156" s="17">
         <v>153</v>
       </c>
@@ -3650,7 +3657,7 @@
         <v>3.2320000000000002</v>
       </c>
     </row>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B157" s="16">
         <v>154</v>
       </c>
@@ -3670,7 +3677,7 @@
         <v>4.8719999999999999</v>
       </c>
     </row>
-    <row r="158" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B158" s="15">
         <v>155</v>
       </c>
@@ -3690,7 +3697,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B159" s="17">
         <v>156</v>
       </c>
@@ -3710,7 +3717,7 @@
         <v>0.30399999999999999</v>
       </c>
     </row>
-    <row r="160" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B160" s="17">
         <v>157</v>
       </c>
@@ -3730,7 +3737,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="161" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B161" s="17">
         <v>158</v>
       </c>
@@ -3750,7 +3757,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="162" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B162" s="17">
         <v>159</v>
       </c>
@@ -3770,7 +3777,7 @@
         <v>1.3620000000000001</v>
       </c>
     </row>
-    <row r="163" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B163" s="17">
         <v>160</v>
       </c>
@@ -3790,7 +3797,7 @@
         <v>1.6439999999999999</v>
       </c>
     </row>
-    <row r="164" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B164" s="16">
         <v>161</v>
       </c>
@@ -3810,7 +3817,7 @@
         <v>2.3519999999999999</v>
       </c>
     </row>
-    <row r="165" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B165" s="15">
         <v>162</v>
       </c>
@@ -3830,7 +3837,7 @@
         <v>0.34599999999999997</v>
       </c>
     </row>
-    <row r="166" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B166" s="17">
         <v>163</v>
       </c>
@@ -3850,7 +3857,7 @@
         <v>0.35799999999999998</v>
       </c>
     </row>
-    <row r="167" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B167" s="17">
         <v>164</v>
       </c>
@@ -3870,7 +3877,7 @@
         <v>0.47599999999999998</v>
       </c>
     </row>
-    <row r="168" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B168" s="17">
         <v>165</v>
       </c>
@@ -3890,7 +3897,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="169" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B169" s="17">
         <v>166</v>
       </c>
@@ -3910,7 +3917,7 @@
         <v>1.278</v>
       </c>
     </row>
-    <row r="170" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B170" s="17">
         <v>167</v>
       </c>
@@ -3930,7 +3937,7 @@
         <v>1.6180000000000001</v>
       </c>
     </row>
-    <row r="171" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B171" s="16">
         <v>168</v>
       </c>
@@ -3950,7 +3957,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="172" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B172" s="15">
         <v>169</v>
       </c>
@@ -3970,7 +3977,7 @@
         <v>0.34899999999999998</v>
       </c>
     </row>
-    <row r="173" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B173" s="17">
         <v>170</v>
       </c>
@@ -3990,7 +3997,7 @@
         <v>0.27400000000000002</v>
       </c>
     </row>
-    <row r="174" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B174" s="17">
         <v>171</v>
       </c>
@@ -4010,7 +4017,7 @@
         <v>0.36599999999999999</v>
       </c>
     </row>
-    <row r="175" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B175" s="17">
         <v>172</v>
       </c>
@@ -4030,7 +4037,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="176" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B176" s="17">
         <v>173</v>
       </c>
@@ -4050,7 +4057,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B177" s="17">
         <v>174</v>
       </c>
@@ -4070,7 +4077,7 @@
         <v>1.214</v>
       </c>
     </row>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B178" s="16">
         <v>175</v>
       </c>
@@ -4090,7 +4097,7 @@
         <v>1.3919999999999999</v>
       </c>
     </row>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B179" s="15">
         <v>176</v>
       </c>
@@ -4110,7 +4117,7 @@
         <v>0.34599999999999997</v>
       </c>
     </row>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B180" s="17">
         <v>177</v>
       </c>
@@ -4130,7 +4137,7 @@
         <v>0.56200000000000006</v>
       </c>
     </row>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B181" s="17">
         <v>178</v>
       </c>
@@ -4150,7 +4157,7 @@
         <v>0.76400000000000001</v>
       </c>
     </row>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B182" s="17">
         <v>179</v>
       </c>
@@ -4170,7 +4177,7 @@
         <v>1.6220000000000001</v>
       </c>
     </row>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B183" s="17">
         <v>180</v>
       </c>
@@ -4190,7 +4197,7 @@
         <v>2.8452000000000002</v>
       </c>
     </row>
-    <row r="184" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B184" s="17">
         <v>181</v>
       </c>
@@ -4210,7 +4217,7 @@
         <v>5.1360000000000001</v>
       </c>
     </row>
-    <row r="185" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B185" s="16">
         <v>182</v>
       </c>
@@ -4230,7 +4237,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B186" s="15">
         <v>183</v>
       </c>
@@ -4250,7 +4257,7 @@
         <v>0.371</v>
       </c>
     </row>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B187" s="17">
         <v>184</v>
       </c>
@@ -4270,7 +4277,7 @@
         <v>0.54600000000000004</v>
       </c>
     </row>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B188" s="17">
         <v>185</v>
       </c>
@@ -4290,7 +4297,7 @@
         <v>0.78100000000000003</v>
       </c>
     </row>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B189" s="17">
         <v>186</v>
       </c>
@@ -4310,7 +4317,7 @@
         <v>1.544</v>
       </c>
     </row>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B190" s="17">
         <v>187</v>
       </c>
@@ -4330,7 +4337,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B191" s="17">
         <v>188</v>
       </c>
@@ -4350,7 +4357,7 @@
         <v>5.2320000000000002</v>
       </c>
     </row>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B192" s="16">
         <v>189</v>
       </c>
@@ -4370,7 +4377,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B193" s="15">
         <v>190</v>
       </c>
@@ -4390,7 +4397,7 @@
         <v>0.378</v>
       </c>
     </row>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B194" s="17">
         <v>191</v>
       </c>
@@ -4410,7 +4417,7 @@
         <v>0.50800000000000001</v>
       </c>
     </row>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B195" s="17">
         <v>192</v>
       </c>
@@ -4430,7 +4437,7 @@
         <v>0.73499999999999999</v>
       </c>
     </row>
-    <row r="196" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B196" s="17">
         <v>193</v>
       </c>
@@ -4450,7 +4457,7 @@
         <v>1.3979999999999999</v>
       </c>
     </row>
-    <row r="197" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B197" s="17">
         <v>194</v>
       </c>
@@ -4470,7 +4477,7 @@
         <v>2.488</v>
       </c>
     </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B198" s="17">
         <v>195</v>
       </c>
@@ -4490,7 +4497,7 @@
         <v>4.2560000000000002</v>
       </c>
     </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B199" s="16">
         <v>196</v>
       </c>
@@ -4510,7 +4517,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B200" s="15">
         <v>197</v>
       </c>
@@ -4530,7 +4537,7 @@
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B201" s="17">
         <v>198</v>
       </c>
@@ -4550,7 +4557,7 @@
         <v>0.46700000000000003</v>
       </c>
     </row>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B202" s="17">
         <v>199</v>
       </c>
@@ -4570,7 +4577,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="203" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B203" s="17">
         <v>200</v>
       </c>
@@ -4590,7 +4597,7 @@
         <v>1.546</v>
       </c>
     </row>
-    <row r="204" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B204" s="17">
         <v>201</v>
       </c>
@@ -4610,7 +4617,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="205" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B205" s="17">
         <v>202</v>
       </c>
@@ -4630,7 +4637,7 @@
         <v>5.4480000000000004</v>
       </c>
     </row>
-    <row r="206" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B206" s="16">
         <v>203</v>
       </c>
@@ -4650,7 +4657,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="207" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B207" s="15">
         <v>204</v>
       </c>
@@ -4670,7 +4677,7 @@
         <v>0.372</v>
       </c>
     </row>
-    <row r="208" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B208" s="17">
         <v>205</v>
       </c>
@@ -4690,7 +4697,7 @@
         <v>0.54600000000000004</v>
       </c>
     </row>
-    <row r="209" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B209" s="17">
         <v>206</v>
       </c>
@@ -4710,7 +4717,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="210" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B210" s="17">
         <v>207</v>
       </c>
@@ -4730,7 +4737,7 @@
         <v>1.458</v>
       </c>
     </row>
-    <row r="211" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B211" s="17">
         <v>208</v>
       </c>
@@ -4750,7 +4757,7 @@
         <v>2.6080000000000001</v>
       </c>
     </row>
-    <row r="212" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B212" s="17">
         <v>209</v>
       </c>
@@ -4770,7 +4777,7 @@
         <v>4.4160000000000004</v>
       </c>
     </row>
-    <row r="213" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B213" s="16">
         <v>210</v>
       </c>
@@ -4790,7 +4797,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="214" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B214" s="15">
         <v>211</v>
       </c>
@@ -4810,7 +4817,7 @@
         <v>0.374</v>
       </c>
     </row>
-    <row r="215" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B215" s="17">
         <v>212</v>
       </c>
@@ -4830,7 +4837,7 @@
         <v>0.48699999999999999</v>
       </c>
     </row>
-    <row r="216" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B216" s="17">
         <v>213</v>
       </c>
@@ -4850,7 +4857,7 @@
         <v>0.66300000000000003</v>
       </c>
     </row>
-    <row r="217" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B217" s="17">
         <v>214</v>
       </c>
@@ -4870,7 +4877,7 @@
         <v>1.248</v>
       </c>
     </row>
-    <row r="218" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B218" s="17">
         <v>215</v>
       </c>
@@ -4890,7 +4897,7 @@
         <v>2.476</v>
       </c>
     </row>
-    <row r="219" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B219" s="17">
         <v>216</v>
       </c>
@@ -4910,7 +4917,7 @@
         <v>4.7439999999999998</v>
       </c>
     </row>
-    <row r="220" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B220" s="16">
         <v>217</v>
       </c>
@@ -4930,7 +4937,7 @@
         <v>6.8999999999999995</v>
       </c>
     </row>
-    <row r="221" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B221" s="15">
         <v>218</v>
       </c>
@@ -4950,7 +4957,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="222" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B222" s="17">
         <v>219</v>
       </c>
@@ -4970,7 +4977,7 @@
         <v>0.49199999999999999</v>
       </c>
     </row>
-    <row r="223" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B223" s="17">
         <v>220</v>
       </c>
@@ -4990,7 +4997,7 @@
         <v>0.70899999999999996</v>
       </c>
     </row>
-    <row r="224" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B224" s="17">
         <v>221</v>
       </c>
@@ -5010,7 +5017,7 @@
         <v>1.252</v>
       </c>
     </row>
-    <row r="225" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B225" s="17">
         <v>222</v>
       </c>
@@ -5030,7 +5037,7 @@
         <v>2.512</v>
       </c>
     </row>
-    <row r="226" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B226" s="17">
         <v>223</v>
       </c>
@@ -5050,7 +5057,7 @@
         <v>4.3840000000000003</v>
       </c>
     </row>
-    <row r="227" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B227" s="16">
         <v>224</v>
       </c>
@@ -5070,7 +5077,7 @@
         <v>5.8999999999999995</v>
       </c>
     </row>
-    <row r="228" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B228" s="15">
         <v>225</v>
       </c>
@@ -5090,7 +5097,7 @@
         <v>0.36399999999999999</v>
       </c>
     </row>
-    <row r="229" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B229" s="17">
         <v>226</v>
       </c>
@@ -5110,7 +5117,7 @@
         <v>0.436</v>
       </c>
     </row>
-    <row r="230" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B230" s="17">
         <v>227</v>
       </c>
@@ -5130,7 +5137,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="231" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B231" s="17">
         <v>228</v>
       </c>
@@ -5150,7 +5157,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="232" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B232" s="17">
         <v>229</v>
       </c>
@@ -5170,7 +5177,7 @@
         <v>2.1320000000000001</v>
       </c>
     </row>
-    <row r="233" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B233" s="17">
         <v>230</v>
       </c>
@@ -5190,7 +5197,7 @@
         <v>3.7280000000000002</v>
       </c>
     </row>
-    <row r="234" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B234" s="16">
         <v>231</v>
       </c>
@@ -5210,7 +5217,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="235" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B235" s="15">
         <v>232</v>
       </c>
@@ -5230,7 +5237,7 @@
         <v>0.45300000000000001</v>
       </c>
     </row>
-    <row r="236" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B236" s="17">
         <v>233</v>
       </c>
@@ -5250,7 +5257,7 @@
         <v>0.42899999999999999</v>
       </c>
     </row>
-    <row r="237" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B237" s="17">
         <v>234</v>
       </c>
@@ -5270,7 +5277,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="238" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B238" s="17">
         <v>235</v>
       </c>
@@ -5290,7 +5297,7 @@
         <v>1.304</v>
       </c>
     </row>
-    <row r="239" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B239" s="17">
         <v>236</v>
       </c>
@@ -5310,7 +5317,7 @@
         <v>2.4390000000000001</v>
       </c>
     </row>
-    <row r="240" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B240" s="17">
         <v>237</v>
       </c>
@@ -5330,7 +5337,7 @@
         <v>3.8639999999999999</v>
       </c>
     </row>
-    <row r="241" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B241" s="16">
         <v>238</v>
       </c>
@@ -5350,7 +5357,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="242" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B242" s="15">
         <v>239</v>
       </c>
@@ -5370,7 +5377,7 @@
         <v>0.46100000000000002</v>
       </c>
     </row>
-    <row r="243" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B243" s="17">
         <v>240</v>
       </c>
@@ -5390,7 +5397,7 @@
         <v>0.439</v>
       </c>
     </row>
-    <row r="244" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B244" s="17">
         <v>241</v>
       </c>
@@ -5410,7 +5417,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="245" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B245" s="17">
         <v>242</v>
       </c>
@@ -5430,7 +5437,7 @@
         <v>1.256</v>
       </c>
     </row>
-    <row r="246" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B246" s="17">
         <v>243</v>
       </c>
@@ -5450,7 +5457,7 @@
         <v>2.5680000000000001</v>
       </c>
     </row>
-    <row r="247" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B247" s="17">
         <v>244</v>
       </c>
@@ -5470,7 +5477,7 @@
         <v>3.8559999999999999</v>
       </c>
     </row>
-    <row r="248" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B248" s="16">
         <v>245</v>
       </c>
@@ -5490,7 +5497,7 @@
         <v>5.7439999999999998</v>
       </c>
     </row>
-    <row r="249" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B249" s="15">
         <v>246</v>
       </c>
@@ -5510,7 +5517,7 @@
         <v>0.46300000000000002</v>
       </c>
     </row>
-    <row r="250" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B250" s="17">
         <v>247</v>
       </c>
@@ -5530,7 +5537,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="251" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B251" s="17">
         <v>248</v>
       </c>
@@ -5550,7 +5557,7 @@
         <v>0.32800000000000001</v>
       </c>
     </row>
-    <row r="252" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B252" s="17">
         <v>249</v>
       </c>
@@ -5570,7 +5577,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="253" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B253" s="17">
         <v>250</v>
       </c>
@@ -5590,7 +5597,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="254" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B254" s="17">
         <v>251</v>
       </c>
@@ -5610,7 +5617,7 @@
         <v>2.5760000000000001</v>
       </c>
     </row>
-    <row r="255" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B255" s="16">
         <v>252</v>
       </c>
@@ -5630,7 +5637,7 @@
         <v>4.056</v>
       </c>
     </row>
-    <row r="256" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B256" s="15">
         <v>253</v>
       </c>
@@ -5653,7 +5660,7 @@
       <c r="K256" s="14"/>
       <c r="O256" s="14"/>
     </row>
-    <row r="257" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B257" s="17">
         <v>254</v>
       </c>
@@ -5675,7 +5682,7 @@
       <c r="K257" s="14"/>
       <c r="O257" s="14"/>
     </row>
-    <row r="258" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B258" s="17">
         <v>255</v>
       </c>
@@ -5697,7 +5704,7 @@
       <c r="K258" s="14"/>
       <c r="O258" s="14"/>
     </row>
-    <row r="259" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B259" s="17">
         <v>256</v>
       </c>
@@ -5719,7 +5726,7 @@
       <c r="K259" s="14"/>
       <c r="O259" s="14"/>
     </row>
-    <row r="260" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B260" s="17">
         <v>257</v>
       </c>
@@ -5741,7 +5748,7 @@
       <c r="K260" s="14"/>
       <c r="O260" s="14"/>
     </row>
-    <row r="261" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B261" s="17">
         <v>258</v>
       </c>
@@ -5763,7 +5770,7 @@
       <c r="K261" s="14"/>
       <c r="O261" s="14"/>
     </row>
-    <row r="262" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B262" s="16">
         <v>259</v>
       </c>
@@ -5785,7 +5792,7 @@
       <c r="K262" s="14"/>
       <c r="O262" s="14"/>
     </row>
-    <row r="263" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B263" s="15">
         <v>260</v>
       </c>
@@ -5805,7 +5812,7 @@
         <v>0.34200000000000003</v>
       </c>
     </row>
-    <row r="264" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B264" s="17">
         <v>261</v>
       </c>
@@ -5825,7 +5832,7 @@
         <v>0.49299999999999999</v>
       </c>
     </row>
-    <row r="265" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B265" s="17">
         <v>262</v>
       </c>
@@ -5845,7 +5852,7 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="266" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B266" s="17">
         <v>263</v>
       </c>
@@ -5865,7 +5872,7 @@
         <v>1.6160000000000001</v>
       </c>
     </row>
-    <row r="267" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B267" s="17">
         <v>264</v>
       </c>
@@ -5885,7 +5892,7 @@
         <v>3.6360000000000001</v>
       </c>
     </row>
-    <row r="268" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B268" s="17">
         <v>265</v>
       </c>
@@ -5905,7 +5912,7 @@
         <v>6.9799999999999995</v>
       </c>
     </row>
-    <row r="269" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B269" s="16">
         <v>266</v>
       </c>
@@ -5925,7 +5932,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="270" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B270" s="15">
         <v>267</v>
       </c>
@@ -5945,7 +5952,7 @@
         <v>0.36499999999999999</v>
       </c>
     </row>
-    <row r="271" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B271" s="17">
         <v>268</v>
       </c>
@@ -5965,7 +5972,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="272" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B272" s="17">
         <v>269</v>
       </c>
@@ -5985,7 +5992,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="273" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B273" s="17">
         <v>270</v>
       </c>
@@ -6005,7 +6012,7 @@
         <v>1.534</v>
       </c>
     </row>
-    <row r="274" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B274" s="17">
         <v>271</v>
       </c>
@@ -6025,7 +6032,7 @@
         <v>3.0760000000000001</v>
       </c>
     </row>
-    <row r="275" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B275" s="17">
         <v>272</v>
       </c>
@@ -6045,7 +6052,7 @@
         <v>5.3500000000000005</v>
       </c>
     </row>
-    <row r="276" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B276" s="16">
         <v>273</v>
       </c>
@@ -6065,7 +6072,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="277" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B277" s="15">
         <v>274</v>
       </c>
@@ -6085,7 +6092,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="278" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B278" s="17">
         <v>275</v>
       </c>
@@ -6105,7 +6112,7 @@
         <v>1.194</v>
       </c>
     </row>
-    <row r="279" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B279" s="17">
         <v>276</v>
       </c>
@@ -6125,7 +6132,7 @@
         <v>1.929</v>
       </c>
     </row>
-    <row r="280" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B280" s="17">
         <v>277</v>
       </c>
@@ -6145,7 +6152,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="281" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B281" s="17">
         <v>278</v>
       </c>
@@ -6165,7 +6172,7 @@
         <v>4.2349999999999994</v>
       </c>
     </row>
-    <row r="282" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B282" s="17">
         <v>279</v>
       </c>
@@ -6185,7 +6192,7 @@
         <v>5.8599999999999994</v>
       </c>
     </row>
-    <row r="283" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B283" s="16">
         <v>280</v>
       </c>
@@ -6205,7 +6212,7 @@
         <v>6.9599999999999991</v>
       </c>
     </row>
-    <row r="284" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B284" s="15">
         <v>281</v>
       </c>
@@ -6225,7 +6232,7 @@
         <v>0.71899999999999997</v>
       </c>
     </row>
-    <row r="285" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B285" s="17">
         <v>282</v>
       </c>
@@ -6245,7 +6252,7 @@
         <v>1.1439999999999999</v>
       </c>
     </row>
-    <row r="286" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B286" s="17">
         <v>283</v>
       </c>
@@ -6265,7 +6272,7 @@
         <v>1.956</v>
       </c>
     </row>
-    <row r="287" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B287" s="17">
         <v>284</v>
       </c>
@@ -6285,7 +6292,7 @@
         <v>2.9119999999999999</v>
       </c>
     </row>
-    <row r="288" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B288" s="17">
         <v>285</v>
       </c>
@@ -6305,7 +6312,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="289" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B289" s="17">
         <v>286</v>
       </c>
@@ -6325,7 +6332,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="290" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B290" s="16">
         <v>287</v>
       </c>
@@ -6345,7 +6352,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="291" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B291" s="15">
         <v>288</v>
       </c>
@@ -6365,7 +6372,7 @@
         <v>0.70199999999999996</v>
       </c>
     </row>
-    <row r="292" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B292" s="17">
         <v>289</v>
       </c>
@@ -6385,7 +6392,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="293" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B293" s="17">
         <v>290</v>
       </c>
@@ -6405,7 +6412,7 @@
         <v>1.8239999999999998</v>
       </c>
     </row>
-    <row r="294" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B294" s="17">
         <v>291</v>
       </c>
@@ -6425,7 +6432,7 @@
         <v>2.6320000000000001</v>
       </c>
     </row>
-    <row r="295" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B295" s="17">
         <v>292</v>
       </c>
@@ -6445,7 +6452,7 @@
         <v>3.5199999999999996</v>
       </c>
     </row>
-    <row r="296" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B296" s="17">
         <v>293</v>
       </c>
@@ -6465,7 +6472,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="297" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B297" s="16">
         <v>294</v>
       </c>
@@ -6485,7 +6492,7 @@
         <v>4.7299999999999995</v>
       </c>
     </row>
-    <row r="298" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B298" s="15">
         <v>295</v>
       </c>
@@ -6505,7 +6512,7 @@
         <v>0.74199999999999999</v>
       </c>
     </row>
-    <row r="299" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B299" s="17">
         <v>296</v>
       </c>
@@ -6525,7 +6532,7 @@
         <v>1.0820000000000001</v>
       </c>
     </row>
-    <row r="300" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B300" s="17">
         <v>297</v>
       </c>
@@ -6545,7 +6552,7 @@
         <v>1.857</v>
       </c>
     </row>
-    <row r="301" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B301" s="17">
         <v>298</v>
       </c>
@@ -6565,7 +6572,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="302" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B302" s="17">
         <v>299</v>
       </c>
@@ -6585,7 +6592,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="303" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B303" s="17">
         <v>300</v>
       </c>
@@ -6605,7 +6612,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="304" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B304" s="16">
         <v>301</v>
       </c>
@@ -6625,7 +6632,7 @@
         <v>8.7299999999999986</v>
       </c>
     </row>
-    <row r="305" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B305" s="15">
         <v>302</v>
       </c>
@@ -6645,7 +6652,7 @@
         <v>0.75800000000000001</v>
       </c>
     </row>
-    <row r="306" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B306" s="17">
         <v>303</v>
       </c>
@@ -6665,7 +6672,7 @@
         <v>1.0840000000000001</v>
       </c>
     </row>
-    <row r="307" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B307" s="17">
         <v>304</v>
       </c>
@@ -6685,7 +6692,7 @@
         <v>1.7489999999999999</v>
       </c>
     </row>
-    <row r="308" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B308" s="17">
         <v>305</v>
       </c>
@@ -6705,7 +6712,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="309" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B309" s="17">
         <v>306</v>
       </c>
@@ -6725,7 +6732,7 @@
         <v>4.2479999999999993</v>
       </c>
     </row>
-    <row r="310" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B310" s="17">
         <v>307</v>
       </c>
@@ -6745,7 +6752,7 @@
         <v>6.6300000000000008</v>
       </c>
     </row>
-    <row r="311" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B311" s="16">
         <v>308</v>
       </c>
@@ -6765,7 +6772,7 @@
         <v>7.26</v>
       </c>
     </row>
-    <row r="312" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B312" s="15">
         <v>309</v>
       </c>
@@ -6785,7 +6792,7 @@
         <v>0.71699999999999997</v>
       </c>
     </row>
-    <row r="313" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B313" s="17">
         <v>310</v>
       </c>
@@ -6805,7 +6812,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="314" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B314" s="17">
         <v>311</v>
       </c>
@@ -6825,7 +6832,7 @@
         <v>1.8359999999999999</v>
       </c>
     </row>
-    <row r="315" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B315" s="17">
         <v>312</v>
       </c>
@@ -6845,7 +6852,7 @@
         <v>3.7719999999999998</v>
       </c>
     </row>
-    <row r="316" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B316" s="17">
         <v>313</v>
       </c>
@@ -6865,7 +6872,7 @@
         <v>6.048</v>
       </c>
     </row>
-    <row r="317" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B317" s="17">
         <v>314</v>
       </c>
@@ -6885,7 +6892,7 @@
         <v>11.267999999999999</v>
       </c>
     </row>
-    <row r="318" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B318" s="16">
         <v>315</v>
       </c>
@@ -6905,7 +6912,7 @@
         <v>17.68</v>
       </c>
     </row>
-    <row r="319" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B319" s="15">
         <v>316</v>
       </c>
@@ -6925,7 +6932,7 @@
         <v>0.72599999999999998</v>
       </c>
     </row>
-    <row r="320" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B320" s="17">
         <v>317</v>
       </c>
@@ -6945,7 +6952,7 @@
         <v>1.0660000000000001</v>
       </c>
     </row>
-    <row r="321" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B321" s="17">
         <v>318</v>
       </c>
@@ -6965,7 +6972,7 @@
         <v>1.839</v>
       </c>
     </row>
-    <row r="322" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B322" s="17">
         <v>319</v>
       </c>
@@ -6985,7 +6992,7 @@
         <v>3.496</v>
       </c>
     </row>
-    <row r="323" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B323" s="17">
         <v>320</v>
       </c>
@@ -7005,7 +7012,7 @@
         <v>5.306</v>
       </c>
     </row>
-    <row r="324" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B324" s="17">
         <v>321</v>
       </c>
@@ -7025,7 +7032,7 @@
         <v>9.2639999999999993</v>
       </c>
     </row>
-    <row r="325" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B325" s="16">
         <v>322</v>
       </c>
@@ -7045,7 +7052,7 @@
         <v>10.95</v>
       </c>
     </row>
-    <row r="326" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B326" s="15">
         <v>323</v>
       </c>
@@ -7065,7 +7072,7 @@
         <v>0.72599999999999998</v>
       </c>
     </row>
-    <row r="327" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B327" s="17">
         <v>324</v>
       </c>
@@ -7085,7 +7092,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="328" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B328" s="17">
         <v>325</v>
       </c>
@@ -7105,7 +7112,7 @@
         <v>1.7729999999999999</v>
       </c>
     </row>
-    <row r="329" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B329" s="17">
         <v>326</v>
       </c>
@@ -7125,7 +7132,7 @@
         <v>3.2839999999999998</v>
       </c>
     </row>
-    <row r="330" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B330" s="17">
         <v>327</v>
       </c>
@@ -7145,7 +7152,7 @@
         <v>5.0049999999999999</v>
       </c>
     </row>
-    <row r="331" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B331" s="17">
         <v>328</v>
       </c>
@@ -7165,7 +7172,7 @@
         <v>8.4239999999999995</v>
       </c>
     </row>
-    <row r="332" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B332" s="16">
         <v>329</v>
       </c>
@@ -7185,7 +7192,7 @@
         <v>8.6399999999999988</v>
       </c>
     </row>
-    <row r="333" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B333" s="15">
         <v>330</v>
       </c>
@@ -7205,7 +7212,7 @@
         <v>0.50700000000000001</v>
       </c>
     </row>
-    <row r="334" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B334" s="17">
         <v>331</v>
       </c>
@@ -7225,7 +7232,7 @@
         <v>0.71099999999999997</v>
       </c>
     </row>
-    <row r="335" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B335" s="17">
         <v>332</v>
       </c>
@@ -7245,7 +7252,7 @@
         <v>1.3939999999999999</v>
       </c>
     </row>
-    <row r="336" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B336" s="17">
         <v>333</v>
       </c>
@@ -7265,7 +7272,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="337" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B337" s="17">
         <v>334</v>
       </c>
@@ -7285,7 +7292,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="338" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B338" s="17">
         <v>335</v>
       </c>
@@ -7305,7 +7312,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="339" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B339" s="16">
         <v>336</v>
       </c>
@@ -7325,7 +7332,7 @@
         <v>5.9499999999999993</v>
       </c>
     </row>
-    <row r="340" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B340" s="15">
         <v>337</v>
       </c>
@@ -7345,7 +7352,7 @@
         <v>0.55700000000000005</v>
       </c>
     </row>
-    <row r="341" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B341" s="17">
         <v>338</v>
       </c>
@@ -7365,7 +7372,7 @@
         <v>0.73699999999999999</v>
       </c>
     </row>
-    <row r="342" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B342" s="17">
         <v>339</v>
       </c>
@@ -7385,7 +7392,7 @@
         <v>1.542</v>
       </c>
     </row>
-    <row r="343" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B343" s="17">
         <v>340</v>
       </c>
@@ -7405,7 +7412,7 @@
         <v>3.1680000000000001</v>
       </c>
     </row>
-    <row r="344" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B344" s="17">
         <v>341</v>
       </c>
@@ -7425,7 +7432,7 @@
         <v>4.2750000000000004</v>
       </c>
     </row>
-    <row r="345" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B345" s="17">
         <v>342</v>
       </c>
@@ -7445,7 +7452,7 @@
         <v>6.4700000000000006</v>
       </c>
     </row>
-    <row r="346" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B346" s="16">
         <v>343</v>
       </c>
@@ -7465,7 +7472,7 @@
         <v>6.8999999999999995</v>
       </c>
     </row>
-    <row r="347" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B347" s="15">
         <v>344</v>
       </c>
@@ -7485,7 +7492,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="348" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B348" s="17">
         <v>345</v>
       </c>
@@ -7505,7 +7512,7 @@
         <v>0.63500000000000001</v>
       </c>
     </row>
-    <row r="349" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B349" s="17">
         <v>346</v>
       </c>
@@ -7525,7 +7532,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="350" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B350" s="17">
         <v>347</v>
       </c>
@@ -7545,7 +7552,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="351" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B351" s="17">
         <v>348</v>
       </c>
@@ -7565,7 +7572,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="352" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B352" s="17">
         <v>349</v>
       </c>
@@ -7585,7 +7592,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="353" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B353" s="16">
         <v>350</v>
       </c>
@@ -7605,7 +7612,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="354" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B354" s="15">
         <v>351</v>
       </c>
@@ -7625,7 +7632,7 @@
         <v>0.56100000000000005</v>
       </c>
     </row>
-    <row r="355" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B355" s="17">
         <v>352</v>
       </c>
@@ -7645,7 +7652,7 @@
         <v>0.47799999999999998</v>
       </c>
     </row>
-    <row r="356" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B356" s="17">
         <v>353</v>
       </c>
@@ -7665,7 +7672,7 @@
         <v>0.58399999999999996</v>
       </c>
     </row>
-    <row r="357" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B357" s="17">
         <v>354</v>
       </c>
@@ -7685,7 +7692,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="358" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B358" s="17">
         <v>355</v>
       </c>
@@ -7705,7 +7712,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="359" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B359" s="17">
         <v>356</v>
       </c>
@@ -7725,7 +7732,7 @@
         <v>5.0600000000000005</v>
       </c>
     </row>
-    <row r="360" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B360" s="16">
         <v>357</v>
       </c>
@@ -7745,7 +7752,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="361" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B361" s="15">
         <v>358</v>
       </c>
@@ -7765,7 +7772,7 @@
         <v>0.60699999999999998</v>
       </c>
     </row>
-    <row r="362" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B362" s="17">
         <v>359</v>
       </c>
@@ -7785,7 +7792,7 @@
         <v>0.67400000000000004</v>
       </c>
     </row>
-    <row r="363" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B363" s="17">
         <v>360</v>
       </c>
@@ -7805,7 +7812,7 @@
         <v>1.1519999999999999</v>
       </c>
     </row>
-    <row r="364" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B364" s="17">
         <v>361</v>
       </c>
@@ -7825,7 +7832,7 @@
         <v>2.9239999999999999</v>
       </c>
     </row>
-    <row r="365" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B365" s="17">
         <v>362</v>
       </c>
@@ -7845,7 +7852,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="366" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B366" s="17">
         <v>363</v>
       </c>
@@ -7865,7 +7872,7 @@
         <v>9.43</v>
       </c>
     </row>
-    <row r="367" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B367" s="16">
         <v>364</v>
       </c>
@@ -7885,7 +7892,7 @@
         <v>9.370000000000001</v>
       </c>
     </row>
-    <row r="368" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B368" s="15">
         <v>365</v>
       </c>
@@ -7905,7 +7912,7 @@
         <v>0.64600000000000002</v>
       </c>
     </row>
-    <row r="369" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B369" s="17">
         <v>366</v>
       </c>
@@ -7925,7 +7932,7 @@
         <v>0.69099999999999995</v>
       </c>
     </row>
-    <row r="370" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B370" s="17">
         <v>367</v>
       </c>
@@ -7945,7 +7952,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="371" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B371" s="17">
         <v>368</v>
       </c>
@@ -7965,7 +7972,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="372" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B372" s="17">
         <v>369</v>
       </c>
@@ -7985,7 +7992,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="373" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B373" s="17">
         <v>370</v>
       </c>
@@ -8005,7 +8012,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="374" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B374" s="16">
         <v>371</v>
       </c>
